--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3547,7 +3547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>147</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -627,6 +627,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -4959,7 +4963,7 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>74</v>
@@ -4967,10 +4971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4996,10 +5000,10 @@
         <v>91</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5030,7 +5034,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -5048,7 +5052,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5068,10 +5072,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5169,10 +5173,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5201,7 +5205,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5213,7 +5217,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5252,7 +5256,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5272,17 +5276,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5304,7 +5308,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5355,7 +5359,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5375,17 +5379,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5407,7 +5411,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5458,7 +5462,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5478,17 +5482,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5510,7 +5514,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5561,7 +5565,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5581,17 +5585,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
@@ -5613,7 +5617,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5664,7 +5668,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5684,10 +5688,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5710,11 +5714,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5765,7 +5769,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5785,10 +5789,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5815,7 +5819,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5866,7 +5870,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5886,17 +5890,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5918,7 +5922,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5969,7 +5973,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5989,17 +5993,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -6017,11 +6021,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6072,7 +6076,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6092,17 +6096,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6124,7 +6128,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6175,7 +6179,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6195,10 +6199,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6221,10 +6225,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6276,7 +6280,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6288,7 +6292,7 @@
         <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>74</v>
@@ -6296,10 +6300,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6322,7 +6326,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6355,7 +6359,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6373,7 +6377,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6393,10 +6397,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6419,7 +6423,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6472,7 +6476,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6492,10 +6496,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6518,7 +6522,7 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6551,25 +6555,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6589,10 +6593,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6648,25 +6652,25 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6686,10 +6690,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6712,13 +6716,13 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6769,7 +6773,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6789,10 +6793,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6890,17 +6894,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
@@ -6922,7 +6926,7 @@
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6973,7 +6977,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6993,17 +6997,17 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
@@ -7021,11 +7025,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7076,7 +7080,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7096,17 +7100,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
@@ -7124,11 +7128,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7179,7 +7183,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7199,10 +7203,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7229,12 +7233,12 @@
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
@@ -7260,7 +7264,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7278,7 +7282,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7298,17 +7302,17 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>75</v>
@@ -7326,11 +7330,11 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7381,7 +7385,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7401,17 +7405,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
@@ -7429,11 +7433,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7484,7 +7488,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7504,17 +7508,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
@@ -7532,11 +7536,11 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7587,7 +7591,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7607,17 +7611,17 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>75</v>
@@ -7635,11 +7639,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7690,7 +7694,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7710,10 +7714,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7736,10 +7740,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -7791,7 +7795,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7811,10 +7815,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7912,17 +7916,17 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
@@ -7944,7 +7948,7 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7995,7 +7999,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8015,17 +8019,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -8043,11 +8047,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8098,7 +8102,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8118,17 +8122,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -8146,11 +8150,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8201,7 +8205,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8221,10 +8225,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8251,12 +8255,12 @@
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
@@ -8282,7 +8286,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8300,7 +8304,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8320,17 +8324,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8348,11 +8352,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8403,7 +8407,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8423,17 +8427,17 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
@@ -8451,11 +8455,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8506,7 +8510,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8526,17 +8530,17 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
@@ -8554,11 +8558,11 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8609,7 +8613,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8629,17 +8633,17 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>75</v>
@@ -8657,11 +8661,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8712,7 +8716,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8732,10 +8736,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8758,7 +8762,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8811,7 +8815,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8831,10 +8835,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8857,7 +8861,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8890,25 +8894,25 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8928,10 +8932,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8954,13 +8958,13 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9011,7 +9015,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9031,10 +9035,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9132,10 +9136,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9233,10 +9237,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9334,10 +9338,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9435,10 +9439,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9538,10 +9542,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9641,10 +9645,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9744,10 +9748,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9847,10 +9851,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9948,10 +9952,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9985,7 +9989,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>74</v>
@@ -10007,7 +10011,7 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -10025,7 +10029,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10045,10 +10049,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10071,7 +10075,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10124,7 +10128,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -10144,10 +10148,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10170,7 +10174,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10223,7 +10227,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10243,10 +10247,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10269,7 +10273,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10322,7 +10326,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10342,10 +10346,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10368,7 +10372,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10421,7 +10425,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10441,10 +10445,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10467,7 +10471,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10520,7 +10524,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10540,10 +10544,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10566,7 +10570,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10619,7 +10623,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10639,10 +10643,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10665,7 +10669,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10718,7 +10722,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10738,10 +10742,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10764,7 +10768,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10817,7 +10821,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10837,10 +10841,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10863,7 +10867,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10916,7 +10920,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10936,10 +10940,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10962,13 +10966,13 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11019,7 +11023,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11039,10 +11043,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11140,10 +11144,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11241,10 +11245,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11342,10 +11346,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11443,10 +11447,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11546,10 +11550,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11649,10 +11653,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11752,10 +11756,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11855,10 +11859,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11956,10 +11960,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11993,7 +11997,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>74</v>
@@ -12015,7 +12019,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -12033,7 +12037,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12053,10 +12057,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12079,7 +12083,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12132,7 +12136,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -12152,10 +12156,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12253,10 +12257,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12354,10 +12358,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12455,10 +12459,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12556,10 +12560,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12659,10 +12663,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12762,10 +12766,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12865,10 +12869,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12968,10 +12972,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13069,10 +13073,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13102,7 +13106,7 @@
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
@@ -13128,7 +13132,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>74</v>
@@ -13146,7 +13150,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13166,10 +13170,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13203,7 +13207,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>74</v>
@@ -13225,7 +13229,7 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
@@ -13243,7 +13247,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13263,10 +13267,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13322,7 +13326,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>74</v>
@@ -13340,7 +13344,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13360,10 +13364,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13439,7 +13443,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13459,10 +13463,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13485,7 +13489,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13538,7 +13542,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13558,10 +13562,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13584,7 +13588,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13637,7 +13641,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
